--- a/labs/harvest/lab-harvest.xlsx
+++ b/labs/harvest/lab-harvest.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Excercise I" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Exercise I" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Exercise II" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Exercise III" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -22,182 +21,36 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
-  <si>
-    <t xml:space="preserve">Year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pythons</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">lambda (</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">λ</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">t</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">= </t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">N</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">t</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">N</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">t-1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">H (pythons harvested)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Geometric or logistic? (question 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">r (question 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d (question 3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">h (question 4)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+  <si>
+    <t xml:space="preserve">Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N without harvest (question 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sustainable harvest (H) (question 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rmax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N at MSY (question 3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSY (question 4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N with harvest (question 5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harvest (Ht) plan to achieve MSY (question 5)</t>
   </si>
   <si>
     <t xml:space="preserve">Leave this cell blank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leave blank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N without harvest (question 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sustainable harvest (H) (question 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rmax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N at MSY (question 3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSY (question 4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N with harvest (question 5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harvest (Ht) plan to achieve MSY (question 5)</t>
   </si>
   <si>
     <t xml:space="preserve">Question 2</t>
@@ -244,7 +97,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -266,23 +119,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <vertAlign val="subscript"/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -357,10 +193,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -368,12 +208,8 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -472,37 +308,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -575,245 +411,6 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
-  <sheetFormatPr defaultColWidth="8.578125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="19.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="12.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="44"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
-        <v>2017</v>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
-        <v>2018</v>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
-        <v>2019</v>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
-        <v>2020</v>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>156.25</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>390.625</v>
-      </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>976.5625</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>2441.40625</v>
-      </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>6103.515625</v>
-      </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B10" s="4"/>
-      <c r="D10" s="3"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B11" s="4"/>
-      <c r="D11" s="3"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="n">
-        <v>2027</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="D12" s="3"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="n">
-        <v>2028</v>
-      </c>
-      <c r="B13" s="4"/>
-      <c r="D13" s="3"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="n">
-        <v>2029</v>
-      </c>
-      <c r="B14" s="4"/>
-      <c r="D14" s="3"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="n">
-        <v>2030</v>
-      </c>
-      <c r="B15" s="4"/>
-      <c r="D15" s="3"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="n">
-        <v>2031</v>
-      </c>
-      <c r="B16" s="4"/>
-      <c r="D16" s="3"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="n">
-        <v>2032</v>
-      </c>
-      <c r="B17" s="4"/>
-      <c r="D17" s="3"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="n">
-        <v>2033</v>
-      </c>
-      <c r="B18" s="4"/>
-      <c r="D18" s="3"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="n">
-        <v>2034</v>
-      </c>
-      <c r="B19" s="4"/>
-      <c r="D19" s="3"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="n">
-        <v>2035</v>
-      </c>
-      <c r="B20" s="4"/>
-      <c r="D20" s="3"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="n">
-        <v>2036</v>
-      </c>
-      <c r="B21" s="4"/>
-      <c r="D21" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
   <dimension ref="A1:L44"/>
   <sheetFormatPr defaultColWidth="8.578125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -828,423 +425,423 @@
   <sheetData>
     <row r="1" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>12</v>
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>18</v>
+        <v>4</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="C2" s="4"/>
+      <c r="C2" s="5"/>
       <c r="E2" s="1" t="n">
         <v>0.32</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>2000</v>
       </c>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
       <c r="K2" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="L2" s="3"/>
+      <c r="L2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="3"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="3"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="3"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="3"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="3"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="3"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="6"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="3"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="3"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="3"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="6"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="3"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="3"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="6"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="3"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="3"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="6"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="3"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="6"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="3"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="6"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="K18" s="4"/>
-      <c r="L18" s="3"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="6"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="3"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="6"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="3"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="6"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="3"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="6"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="3"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="6"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="3"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="6"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="3"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="6"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="3"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="6"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="3"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="6"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="K27" s="4"/>
-      <c r="L27" s="3"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="6"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="3"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="6"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="3"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="6"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="K30" s="4"/>
-      <c r="L30" s="3"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="6"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="3"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="6"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="3"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="6"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="K33" s="4"/>
-      <c r="L33" s="3"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="6"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="K34" s="4"/>
-      <c r="L34" s="3"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="6"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="3"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="6"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="K36" s="4"/>
-      <c r="L36" s="3"/>
+      <c r="B36" s="5"/>
+      <c r="C36" s="5"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="6"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="K37" s="4"/>
-      <c r="L37" s="3"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="6"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="3"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="6"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="K39" s="4"/>
-      <c r="L39" s="3"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="6"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="K40" s="4"/>
-      <c r="L40" s="3"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="6"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="K41" s="4"/>
-      <c r="L41" s="3"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+      <c r="K41" s="5"/>
+      <c r="L41" s="6"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="K42" s="4"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="K42" s="5"/>
       <c r="L42" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1257,7 +854,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -1276,45 +873,45 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I1" s="8" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B3" s="3"/>
+      <c r="B3" s="6"/>
       <c r="D3" s="1" t="n">
         <v>0.95</v>
       </c>
@@ -1327,159 +924,159 @@
       <c r="H3" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B4" s="3"/>
+      <c r="B4" s="6"/>
       <c r="H4" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="B5" s="3"/>
+      <c r="B5" s="6"/>
       <c r="H5" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="B6" s="3"/>
+      <c r="B6" s="6"/>
       <c r="H6" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="B7" s="3"/>
+      <c r="B7" s="6"/>
       <c r="H7" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="B8" s="3"/>
+      <c r="B8" s="6"/>
       <c r="H8" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="B9" s="3"/>
+      <c r="B9" s="6"/>
       <c r="H9" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="B10" s="3"/>
+      <c r="B10" s="6"/>
       <c r="H10" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="B11" s="3"/>
+      <c r="B11" s="6"/>
       <c r="H11" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="B12" s="3"/>
+      <c r="B12" s="6"/>
       <c r="H12" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>110</v>
       </c>
-      <c r="B13" s="3"/>
+      <c r="B13" s="6"/>
       <c r="H13" s="1" t="n">
         <v>110</v>
       </c>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>120</v>
       </c>
-      <c r="B14" s="3"/>
+      <c r="B14" s="6"/>
       <c r="H14" s="1" t="n">
         <v>120</v>
       </c>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>130</v>
       </c>
-      <c r="B15" s="3"/>
+      <c r="B15" s="6"/>
       <c r="H15" s="1" t="n">
         <v>130</v>
       </c>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>140</v>
       </c>
-      <c r="B16" s="3"/>
+      <c r="B16" s="6"/>
       <c r="H16" s="1" t="n">
         <v>140</v>
       </c>
@@ -1491,64 +1088,64 @@
       <c r="A17" s="1" t="n">
         <v>150</v>
       </c>
-      <c r="B17" s="3"/>
+      <c r="B17" s="6"/>
       <c r="H17" s="10" t="n">
         <v>150</v>
       </c>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>160</v>
       </c>
-      <c r="B18" s="3"/>
+      <c r="B18" s="6"/>
       <c r="H18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>170</v>
       </c>
-      <c r="B19" s="3"/>
+      <c r="B19" s="6"/>
       <c r="H19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>180</v>
       </c>
-      <c r="B20" s="3"/>
+      <c r="B20" s="6"/>
       <c r="H20" s="10"/>
       <c r="I20" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>190</v>
       </c>
-      <c r="B21" s="3"/>
+      <c r="B21" s="6"/>
       <c r="H21" s="10"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <v>200</v>
       </c>
-      <c r="B22" s="3"/>
+      <c r="B22" s="6"/>
       <c r="H22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I23" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="3">
